--- a/artfynd/A 26956-2024 artfynd.xlsx
+++ b/artfynd/A 26956-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82265380</v>
+        <v>119033451</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Middagsberget, Jmt</t>
+          <t>Middagsberget Sörbygden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558822.756410222</v>
+        <v>558845</v>
       </c>
       <c r="R2" t="n">
-        <v>6966159.384632845</v>
+        <v>6966269</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-02-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-02-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82265358</v>
+        <v>119033452</v>
       </c>
       <c r="B3" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,49 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Middagsberget, Jmt</t>
+          <t>Middagsberget Sörbygden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558822.756410222</v>
+        <v>558823</v>
       </c>
       <c r="R3" t="n">
-        <v>6966159.384632845</v>
+        <v>6966260</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-02-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-02-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,77 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82265394</v>
+        <v>119033484</v>
       </c>
       <c r="B4" t="n">
-        <v>56990</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102125</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagsberget, Jmt</t>
+          <t>Middagsberget Sörbygden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558822.756410222</v>
+        <v>558575</v>
       </c>
       <c r="R4" t="n">
-        <v>6966159.384632845</v>
+        <v>6966267</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-02-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-02-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82265374</v>
+        <v>119033485</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,53 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagsberget, Jmt</t>
+          <t>Middagsberget Sörbygden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558822.756410222</v>
+        <v>558600</v>
       </c>
       <c r="R5" t="n">
-        <v>6966159.384632845</v>
+        <v>6966242</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-02-19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-02-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119033451</v>
+        <v>119033486</v>
       </c>
       <c r="B6" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,34 +1074,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100011</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Middagsberget Sörbygden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558845</v>
+        <v>558846</v>
       </c>
       <c r="R6" t="n">
-        <v>6966269</v>
+        <v>6966266</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1269,15 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119033484</v>
+        <v>82265358</v>
       </c>
       <c r="B7" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,37 +1183,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Middagsberget Sörbygden, Jmt</t>
+          <t>Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558575</v>
+        <v>558823</v>
       </c>
       <c r="R7" t="n">
-        <v>6966267</v>
+        <v>6966159</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,12 +1249,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2020-02-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2020-02-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,65 +1269,76 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kaj Svahn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kaj Svahn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119033489</v>
+        <v>82265374</v>
       </c>
       <c r="B8" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Middagsberget Sörbygden, Jmt</t>
+          <t>Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558776</v>
+        <v>558823</v>
       </c>
       <c r="R8" t="n">
-        <v>6966254</v>
+        <v>6966159</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,12 +1362,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2020-02-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2020-02-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,65 +1382,72 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kaj Svahn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kaj Svahn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119033485</v>
+        <v>82265394</v>
       </c>
       <c r="B9" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>102125</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Middagsberget Sörbygden, Jmt</t>
+          <t>Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558600</v>
+        <v>558823</v>
       </c>
       <c r="R9" t="n">
-        <v>6966242</v>
+        <v>6966159</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1543,12 +1471,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2020-02-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2020-02-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,65 +1491,76 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kaj Svahn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kaj Svahn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119033452</v>
+        <v>82265354</v>
       </c>
       <c r="B10" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>102613</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Middagsberget Sörbygden, Jmt</t>
+          <t>Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>558823</v>
       </c>
       <c r="R10" t="n">
-        <v>6966260</v>
+        <v>6966159</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,12 +1584,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2020-02-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2020-02-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,27 +1604,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kaj Svahn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kaj Svahn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119033486</v>
+        <v>82265380</v>
       </c>
       <c r="B11" t="n">
-        <v>57190</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,49 +1627,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100011</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Middagsberget Sörbygden, Jmt</t>
+          <t>Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558846</v>
+        <v>558823</v>
       </c>
       <c r="R11" t="n">
-        <v>6966266</v>
+        <v>6966159</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1759,12 +1685,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2020-02-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2020-02-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1779,15 +1705,213 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Kaj Svahn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kaj Svahn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>82265384</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Middagsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>558823</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6966159</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kaj Svahn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kaj Svahn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>119033489</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Middagsberget Sörbygden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>558776</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6966254</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26956-2024 artfynd.xlsx
+++ b/artfynd/A 26956-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033451</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033452</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033484</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033485</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033486</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82265358</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82265374</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1500,6 +1540,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82265394</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1613,6 +1658,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82265354</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1714,6 +1764,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82265380</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1815,6 +1870,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82265384</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1912,8 +1972,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033489</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>